--- a/assets/constructions/examples/ctd_mt2.xlsx
+++ b/assets/constructions/examples/ctd_mt2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,11 +664,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HCN10087L30-I1.00ISOTMVTH</t>
+          <t>HC10087L20-I1.00ISOTMVTH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -694,7 +719,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14x2</t>
+          <t>M10x1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,7 +749,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M10-M40x1</t>
+          <t>M10x1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -733,7 +758,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>8.699999999999999</v>
@@ -743,20 +768,20 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AD2" t="n">
-        <v>58</v>
+        <v>52.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -813,11 +838,30 @@
         </is>
       </c>
       <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>28563.8</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H04030L09-I36UNFTMVTH</t>
+          <t>S06050-I1.25ISOTMVTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -838,39 +882,39 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNF 8-36 2xDo</t>
+          <t>M8x1.25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2A/2B</t>
+          <t>6g/6H</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>36</v>
-      </c>
-      <c r="O3" t="n">
-        <v>36</v>
-      </c>
-      <c r="P3" t="n">
-        <v>36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
@@ -881,27 +925,27 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="AD3" t="n">
-        <v>36.5</v>
+        <v>44.5</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -917,7 +961,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>VTH</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -938,7 +982,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -958,11 +1002,30 @@
         </is>
       </c>
       <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>16327.43</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HC04032L08-I0.50ISOTMVTH</t>
+          <t>HC20199L42-EI11BSPTMVTH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -983,74 +1046,70 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>BSPT55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M4x0,5</t>
+          <t>BSP 1"x11-1.5xD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>M4x0,5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>19.9</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>41.6</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>42.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="AD4" t="n">
-        <v>36.8</v>
+        <v>59.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1087,7 +1146,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,11 +1166,30 @@
         </is>
       </c>
       <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>650.3</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>59784.49</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HC06044L13-EI20BSWTMVTH</t>
+          <t>HC04032L08-I0.50ISOTMVTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1132,40 +1210,44 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WH55</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSW 1/4"x20-2xDo </t>
+          <t>M4x0,5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>20</v>
-      </c>
-      <c r="O5" t="n">
-        <v>20</v>
-      </c>
-      <c r="P5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>M4x0,5</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>BOTH</t>
@@ -1175,27 +1257,27 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>12.7</v>
+        <v>8</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>13.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AD5" t="n">
-        <v>43.7</v>
+        <v>36.8</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1232,7 +1314,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1252,11 +1334,30 @@
         </is>
       </c>
       <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>212.85</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>19568.09</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S10099-I11UNTMVTS</t>
+          <t>H12119L14-EI18NPT-TMVTH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1277,17 +1378,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>NPT60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNC 5/8"x11</t>
+          <t>NPT 3/8"x18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2A/2B</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1296,19 +1397,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -1317,30 +1418,30 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23.09</v>
+        <v>14.1</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>23.1</v>
+        <v>14.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="n">
-        <v>48.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1356,7 +1457,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1377,7 +1478,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1397,6 +1498,25 @@
         </is>
       </c>
       <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>33020.75</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
